--- a/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>VNRX</t>
   </si>
@@ -656,206 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>200</v>
       </c>
       <c r="I8" s="3">
         <v>200</v>
       </c>
       <c r="J8" s="3">
+        <v>200</v>
+      </c>
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>200</v>
       </c>
       <c r="M8" s="3">
         <v>200</v>
@@ -867,23 +871,23 @@
         <v>200</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q8" s="3">
         <v>100</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -947,13 +951,16 @@
       <c r="AP8" s="3">
         <v>0</v>
       </c>
+      <c r="AQ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>500</v>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
@@ -1069,37 +1076,40 @@
       <c r="AP9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>200</v>
       </c>
       <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400</v>
-      </c>
-      <c r="L10" s="3">
-        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>200</v>
@@ -1111,11 +1121,11 @@
         <v>200</v>
       </c>
       <c r="P10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="3">
         <v>2900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2600</v>
       </c>
       <c r="I12" s="3">
         <v>2600</v>
       </c>
       <c r="J12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K12" s="3">
         <v>3500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3100</v>
-      </c>
-      <c r="T12" s="3">
-        <v>3400</v>
       </c>
       <c r="U12" s="3">
         <v>3400</v>
       </c>
       <c r="V12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W12" s="3">
         <v>4200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2500</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>2300</v>
       </c>
       <c r="AF12" s="3">
         <v>2300</v>
       </c>
       <c r="AG12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH12" s="3">
         <v>2900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>2300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>2100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1800</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1700</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>2700</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,28 +1496,31 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1508,23 +1528,23 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1583,8 +1603,8 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>4</v>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>4</v>
@@ -1592,8 +1612,8 @@
       <c r="AM14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1616,7 +1639,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1658,10 +1681,10 @@
         <v>300</v>
       </c>
       <c r="U15" s="3">
+        <v>300</v>
+      </c>
+      <c r="V15" s="3">
         <v>200</v>
-      </c>
-      <c r="V15" s="3">
-        <v>300</v>
       </c>
       <c r="W15" s="3">
         <v>300</v>
@@ -1673,19 +1696,19 @@
         <v>300</v>
       </c>
       <c r="Z15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA15" s="3">
         <v>200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>300</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>200</v>
       </c>
       <c r="AE15" s="3">
         <v>200</v>
@@ -1705,8 +1728,8 @@
       <c r="AJ15" s="3">
         <v>200</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>4</v>
+      <c r="AK15" s="3">
+        <v>200</v>
       </c>
       <c r="AL15" s="3" t="s">
         <v>4</v>
@@ -1714,8 +1737,8 @@
       <c r="AM15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AN15" s="3">
-        <v>0</v>
+      <c r="AN15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AO15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6800</v>
+        <v>4600</v>
       </c>
       <c r="E17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F17" s="3">
         <v>5300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>4200</v>
       </c>
       <c r="AE17" s="3">
         <v>4200</v>
       </c>
       <c r="AF17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AG17" s="3">
         <v>4000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4400</v>
-      </c>
-      <c r="AI17" s="3">
-        <v>4600</v>
       </c>
       <c r="AJ17" s="3">
         <v>4600</v>
       </c>
       <c r="AK17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AL17" s="3">
         <v>4000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3300</v>
-      </c>
-      <c r="AO17" s="3">
-        <v>3500</v>
       </c>
       <c r="AP17" s="3">
         <v>3500</v>
       </c>
+      <c r="AQ17" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5800</v>
       </c>
-      <c r="E18" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-8700</v>
       </c>
       <c r="N18" s="3">
         <v>-8700</v>
       </c>
       <c r="O18" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="P18" s="3">
         <v>-9500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-8000</v>
       </c>
       <c r="R18" s="3">
         <v>-8000</v>
       </c>
       <c r="S18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="T18" s="3">
         <v>-8100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE18" s="3">
         <v>-4200</v>
       </c>
       <c r="AF18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>-4600</v>
       </c>
       <c r="AJ18" s="3">
         <v>-4600</v>
       </c>
       <c r="AK18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="AL18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-3300</v>
-      </c>
-      <c r="AO18" s="3">
-        <v>-3500</v>
       </c>
       <c r="AP18" s="3">
         <v>-3500</v>
       </c>
+      <c r="AQ18" s="3">
+        <v>-3500</v>
+      </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,35 +2085,36 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -2088,65 +2122,65 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>400</v>
       </c>
       <c r="W20" s="3">
         <v>400</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>500</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>200</v>
       </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
@@ -2169,13 +2203,16 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3">
         <v>500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2183,46 +2220,46 @@
         <v>-5400</v>
       </c>
       <c r="E21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-5500</v>
       </c>
       <c r="J21" s="3">
         <v>-5500</v>
       </c>
       <c r="K21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="L21" s="3">
         <v>-6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7000</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-7500</v>
       </c>
       <c r="S21" s="3">
         <v>-7500</v>
@@ -2231,84 +2268,87 @@
         <v>-7500</v>
       </c>
       <c r="U21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="V21" s="3">
         <v>-7800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>100</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -2344,7 +2384,7 @@
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -2415,94 +2455,97 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
-      <c r="AP22" s="3" t="s">
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-5900</v>
       </c>
       <c r="J23" s="3">
         <v>-5900</v>
       </c>
       <c r="K23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="L23" s="3">
         <v>-7100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7800</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-7700</v>
       </c>
       <c r="T23" s="3">
         <v>-7700</v>
       </c>
       <c r="U23" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="V23" s="3">
         <v>-8100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE23" s="3">
         <v>-4200</v>
@@ -2511,37 +2554,40 @@
         <v>-4200</v>
       </c>
       <c r="AG23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,8 +2630,8 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2662,8 +2708,11 @@
       <c r="AP24" s="3">
         <v>0</v>
       </c>
+      <c r="AQ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,91 +2833,94 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-5900</v>
       </c>
       <c r="J26" s="3">
         <v>-5900</v>
       </c>
       <c r="K26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="L26" s="3">
         <v>-7100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7800</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-7700</v>
       </c>
       <c r="T26" s="3">
         <v>-7700</v>
       </c>
       <c r="U26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="V26" s="3">
         <v>-8100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE26" s="3">
         <v>-4200</v>
@@ -2877,120 +2929,123 @@
         <v>-4200</v>
       </c>
       <c r="AG26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-5800</v>
       </c>
       <c r="J27" s="3">
         <v>-5800</v>
       </c>
       <c r="K27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="L27" s="3">
         <v>-7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7700</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-7600</v>
       </c>
       <c r="T27" s="3">
         <v>-7600</v>
       </c>
       <c r="U27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="V27" s="3">
         <v>-8000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE27" s="3">
         <v>-4200</v>
@@ -2999,37 +3054,40 @@
         <v>-4200</v>
       </c>
       <c r="AG27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,35 +3583,38 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -3552,65 +3622,65 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-400</v>
       </c>
       <c r="W32" s="3">
         <v>-400</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>-200</v>
       </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
@@ -3633,96 +3703,99 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3">
         <v>-500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-5800</v>
       </c>
       <c r="J33" s="3">
         <v>-5800</v>
       </c>
       <c r="K33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="L33" s="3">
         <v>-7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7700</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-7600</v>
       </c>
       <c r="T33" s="3">
         <v>-7600</v>
       </c>
       <c r="U33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="V33" s="3">
         <v>-8000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE33" s="3">
         <v>-4200</v>
@@ -3731,37 +3804,40 @@
         <v>-4200</v>
       </c>
       <c r="AG33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,91 +3958,94 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-5800</v>
       </c>
       <c r="J35" s="3">
         <v>-5800</v>
       </c>
       <c r="K35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="L35" s="3">
         <v>-7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7700</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-7600</v>
       </c>
       <c r="T35" s="3">
         <v>-7600</v>
       </c>
       <c r="U35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="V35" s="3">
         <v>-8000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE35" s="3">
         <v>-4200</v>
@@ -3975,164 +4054,170 @@
         <v>-4200</v>
       </c>
       <c r="AG35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>3100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>27900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>33100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>17000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>19700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>18500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>16400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>10100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>16500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>18500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>21700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,8 +4553,11 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4478,50 +4571,50 @@
         <v>300</v>
       </c>
       <c r="G43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
       </c>
       <c r="I43" s="3">
+        <v>200</v>
+      </c>
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>100</v>
       </c>
       <c r="Q43" s="3">
         <v>100</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
@@ -4543,14 +4636,14 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>0</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
@@ -4567,8 +4660,8 @@
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK43" s="3">
-        <v>0</v>
+      <c r="AK43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL43" s="3">
         <v>0</v>
@@ -4585,8 +4678,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,8 +4803,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4716,13 +4815,13 @@
         <v>300</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>300</v>
@@ -4731,228 +4830,234 @@
         <v>300</v>
       </c>
       <c r="J45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
       </c>
       <c r="L45" s="3">
+        <v>400</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>500</v>
       </c>
       <c r="O45" s="3">
         <v>500</v>
       </c>
       <c r="P45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1400</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1500</v>
       </c>
       <c r="W45" s="3">
         <v>1500</v>
       </c>
       <c r="X45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>1100</v>
       </c>
       <c r="AB45" s="3">
         <v>1100</v>
       </c>
       <c r="AC45" s="3">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="AD45" s="3">
         <v>600</v>
       </c>
       <c r="AE45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>700</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>600</v>
       </c>
       <c r="AJ45" s="3">
         <v>600</v>
       </c>
       <c r="AK45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AL45" s="3">
         <v>500</v>
-      </c>
-      <c r="AL45" s="3">
-        <v>400</v>
       </c>
       <c r="AM45" s="3">
         <v>400</v>
       </c>
       <c r="AN45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AO45" s="3">
         <v>500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E46" s="3">
         <v>4500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>3300</v>
       </c>
       <c r="H46" s="3">
         <v>3300</v>
       </c>
       <c r="I46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J46" s="3">
         <v>4100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>26000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>22000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>24400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>29400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>20300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>22200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>22400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>20300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>14900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>10600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>14300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>17000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>19000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>22000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,46 +5178,49 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5800</v>
-      </c>
-      <c r="O48" s="3">
-        <v>6000</v>
       </c>
       <c r="P48" s="3">
         <v>6000</v>
@@ -5121,61 +5229,61 @@
         <v>6000</v>
       </c>
       <c r="R48" s="3">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="S48" s="3">
         <v>5500</v>
       </c>
       <c r="T48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="U48" s="3">
         <v>5600</v>
-      </c>
-      <c r="U48" s="3">
-        <v>5300</v>
       </c>
       <c r="V48" s="3">
         <v>5300</v>
       </c>
       <c r="W48" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="X48" s="3">
         <v>5600</v>
       </c>
       <c r="Y48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Z48" s="3">
         <v>5500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3500</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>3400</v>
       </c>
       <c r="AC48" s="3">
         <v>3400</v>
       </c>
       <c r="AD48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AE48" s="3">
         <v>3100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>3100</v>
       </c>
       <c r="AG48" s="3">
         <v>3100</v>
       </c>
       <c r="AH48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AI48" s="3">
         <v>3200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3300</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>3500</v>
       </c>
       <c r="AK48" s="3">
         <v>3500</v>
@@ -5184,19 +5292,22 @@
         <v>3500</v>
       </c>
       <c r="AM48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AN48" s="3">
         <v>3400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5225,16 +5336,16 @@
         <v>300</v>
       </c>
       <c r="L49" s="3">
+        <v>300</v>
+      </c>
+      <c r="M49" s="3">
         <v>200</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>100</v>
@@ -5246,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="S49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T49" s="3">
         <v>200</v>
@@ -5258,7 +5369,7 @@
         <v>200</v>
       </c>
       <c r="W49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X49" s="3">
         <v>300</v>
@@ -5276,7 +5387,7 @@
         <v>300</v>
       </c>
       <c r="AC49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AD49" s="3">
         <v>400</v>
@@ -5288,7 +5399,7 @@
         <v>400</v>
       </c>
       <c r="AG49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AH49" s="3">
         <v>500</v>
@@ -5297,7 +5408,7 @@
         <v>500</v>
       </c>
       <c r="AJ49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AK49" s="3">
         <v>600</v>
@@ -5315,10 +5426,13 @@
         <v>600</v>
       </c>
       <c r="AP49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AQ49" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,8 +5678,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5605,8 +5725,8 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E54" s="3">
         <v>9000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>30000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>40500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>26100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>26200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>17500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>20700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>19000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>14600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>18400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>21000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>22500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>24700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,109 +6145,110 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>3000</v>
       </c>
       <c r="Q57" s="3">
         <v>3000</v>
       </c>
       <c r="R57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S57" s="3">
         <v>2500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1100</v>
-      </c>
-      <c r="X57" s="3">
-        <v>1500</v>
       </c>
       <c r="Y57" s="3">
         <v>1500</v>
       </c>
       <c r="Z57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AJ57" s="3">
-        <v>400</v>
       </c>
       <c r="AK57" s="3">
         <v>400</v>
@@ -6129,48 +6260,51 @@
         <v>400</v>
       </c>
       <c r="AN57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AO57" s="3">
         <v>600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
         <v>4600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1100</v>
       </c>
       <c r="I58" s="3">
         <v>1100</v>
       </c>
       <c r="J58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1500</v>
       </c>
       <c r="N58" s="3">
         <v>1500</v>
@@ -6179,454 +6313,466 @@
         <v>1500</v>
       </c>
       <c r="P58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>900</v>
-      </c>
-      <c r="X58" s="3">
-        <v>1000</v>
       </c>
       <c r="Y58" s="3">
         <v>1000</v>
       </c>
       <c r="Z58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA58" s="3">
         <v>900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>600</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>500</v>
       </c>
       <c r="AI58" s="3">
         <v>500</v>
       </c>
       <c r="AJ58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK58" s="3">
         <v>700</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>600</v>
       </c>
       <c r="AL58" s="3">
         <v>600</v>
       </c>
       <c r="AM58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AN58" s="3">
         <v>300</v>
-      </c>
-      <c r="AN58" s="3">
-        <v>200</v>
       </c>
       <c r="AO58" s="3">
         <v>200</v>
       </c>
       <c r="AP58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
       </c>
       <c r="I59" s="3">
         <v>400</v>
       </c>
       <c r="J59" s="3">
-        <v>23100</v>
+        <v>400</v>
       </c>
       <c r="K59" s="3">
         <v>23100</v>
       </c>
       <c r="L59" s="3">
+        <v>23100</v>
+      </c>
+      <c r="M59" s="3">
         <v>23200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2500</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>2400</v>
       </c>
       <c r="AC59" s="3">
         <v>2400</v>
       </c>
       <c r="AD59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AE59" s="3">
         <v>2000</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>1400</v>
       </c>
       <c r="AF59" s="3">
         <v>1400</v>
       </c>
       <c r="AG59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH59" s="3">
         <v>900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E60" s="3">
         <v>13600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AO60" s="3">
-        <v>2000</v>
       </c>
       <c r="AP60" s="3">
         <v>2000</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>2000</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E61" s="3">
         <v>7100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>4700</v>
       </c>
       <c r="J61" s="3">
         <v>4700</v>
       </c>
       <c r="K61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L61" s="3">
         <v>4600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3000</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>2900</v>
       </c>
       <c r="AI61" s="3">
         <v>2900</v>
       </c>
       <c r="AJ61" s="3">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="AK61" s="3">
         <v>2400</v>
       </c>
       <c r="AL61" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="AM61" s="3">
         <v>2100</v>
       </c>
       <c r="AN61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AO61" s="3">
         <v>1800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6637,7 +6783,7 @@
         <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G62" s="3">
         <v>400</v>
@@ -6676,28 +6822,28 @@
         <v>400</v>
       </c>
       <c r="S62" s="3">
+        <v>400</v>
+      </c>
+      <c r="T62" s="3">
         <v>500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>200</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>100</v>
       </c>
       <c r="AA62" s="3">
         <v>100</v>
@@ -6717,8 +6863,8 @@
       <c r="AF62" s="3">
         <v>100</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
+      <c r="AG62" s="3">
+        <v>100</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
@@ -6729,8 +6875,8 @@
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK62" s="3">
-        <v>0</v>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL62" s="3">
         <v>0</v>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E66" s="3">
         <v>42400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-267400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-259600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-252900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-246600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-241300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-235000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-229500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-223800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-217900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-202600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-193900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-185500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-176000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-167300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-160000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-152300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-144600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-137000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-129000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-121800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-116300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-110200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-105000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-95700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-89800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-86300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-82100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-77900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-69400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-55700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-51700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-40900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-38000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-32000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-34200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-34600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-31800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-27800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-24900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-21500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-21800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-15600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-7800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-2000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-2600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>31200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>18700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>16600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>21200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,218 +8688,224 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-5800</v>
       </c>
       <c r="J81" s="3">
         <v>-5800</v>
       </c>
       <c r="K81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="L81" s="3">
         <v>-7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7700</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-7600</v>
       </c>
       <c r="T81" s="3">
         <v>-7600</v>
       </c>
       <c r="U81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="V81" s="3">
         <v>-8000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-4200</v>
       </c>
       <c r="AE81" s="3">
         <v>-4200</v>
@@ -8719,37 +8914,40 @@
         <v>-4200</v>
       </c>
       <c r="AG81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,8 +8990,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8801,10 +9000,10 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
@@ -8837,7 +9036,7 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -8873,10 +9072,10 @@
         <v>200</v>
       </c>
       <c r="AC83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD83" s="3">
         <v>100</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>200</v>
       </c>
       <c r="AE83" s="3">
         <v>200</v>
@@ -8900,7 +9099,7 @@
         <v>200</v>
       </c>
       <c r="AL83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AM83" s="3">
         <v>100</v>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>100</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-5400</v>
       </c>
       <c r="J89" s="3">
         <v>-5400</v>
       </c>
       <c r="K89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="L89" s="3">
         <v>-6700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="AL89" s="3">
-        <v>-2800</v>
       </c>
       <c r="AM89" s="3">
         <v>-2800</v>
       </c>
       <c r="AN89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AO89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9705,25 +9926,25 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
@@ -9732,19 +9953,19 @@
         <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
@@ -9753,28 +9974,28 @@
         <v>-100</v>
       </c>
       <c r="W91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-300</v>
       </c>
       <c r="AB91" s="3">
         <v>-300</v>
       </c>
       <c r="AC91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-100</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
@@ -9801,19 +10022,22 @@
         <v>-100</v>
       </c>
       <c r="AM91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,8 +10283,11 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10071,25 +10301,25 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-300</v>
       </c>
       <c r="N94" s="3">
         <v>-300</v>
@@ -10098,19 +10328,19 @@
         <v>-300</v>
       </c>
       <c r="P94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
@@ -10119,28 +10349,28 @@
         <v>-100</v>
       </c>
       <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AB94" s="3">
         <v>-300</v>
       </c>
       <c r="AC94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
@@ -10167,19 +10397,22 @@
         <v>-100</v>
       </c>
       <c r="AM94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,151 +10953,157 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>7600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>20200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>14100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>5200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>9100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>7700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>11900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
@@ -10862,80 +11111,80 @@
         <v>0</v>
       </c>
       <c r="L101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>-100</v>
       </c>
       <c r="N101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>-100</v>
       </c>
       <c r="R101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
         <v>0</v>
       </c>
@@ -10943,137 +11192,143 @@
         <v>0</v>
       </c>
       <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
         <v>100</v>
       </c>
-      <c r="AN101" s="3">
-        <v>0</v>
-      </c>
       <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>9200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-2000</v>
       </c>
     </row>
